--- a/data/instance_pequeno_P4_M6_T4.xlsx
+++ b/data/instance_pequeno_P4_M6_T4.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Custos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demanda_Cor" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Estoque_Cor" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="De_Para_Cores" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +23,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +52,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,42 +428,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -518,7 +513,7 @@
         <v>42.22758236209214</v>
       </c>
       <c r="G4" t="n">
-        <v>48.17334867654848</v>
+        <v>48.17334867654847</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -547,7 +542,7 @@
         <v>46.22911513233984</v>
       </c>
       <c r="H5" t="n">
-        <v>69.96069176347025</v>
+        <v>69.96069176347024</v>
       </c>
     </row>
     <row r="6">
@@ -563,7 +558,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>38.74199848292246</v>
+        <v>38.74199848292247</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
@@ -587,32 +582,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>01/2024</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>02/2024</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>03/2024</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>04/2024</t>
         </is>
@@ -729,17 +724,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>12/2023</t>
         </is>
@@ -820,17 +815,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CUSTO_UNITARIO</t>
         </is>
@@ -911,37 +906,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1046,6 +1041,1604 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>QUANTIDADE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PRAZO_ENTREGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>12268.07041432437</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16498.8749769389</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2701.556994993507</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>45297</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11213.73729654494</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15080.94129162372</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>45329</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2469.381851454668</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>45331</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11954.75649713082</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>45373</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16077.51065690078</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>45371</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2632.562004254396</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>45370</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10959.82420036089</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>45393</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14739.46294275015</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>45411</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2413.467540731806</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>45385</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6435.022201578522</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>16700.93672384519</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>45295</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5901.637109837293</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6751.573627786905</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>17522.48872061256</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>45333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6191.950272024216</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4819.486632223506</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>45367</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12508.10622944521</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>45373</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4420.009794545529</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>45366</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5871.810353610185</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>45390</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>15239.22219662386</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5385.108675505765</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>45412</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11706.25947588156</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>45300</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>9668.807548459987</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>45316</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>4491.956595481869</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>45300</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11387.91345816844</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>45343</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9405.869042319029</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>45345</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4369.800026437928</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>45336</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12075.09571110682</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>45374</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>9973.448546947942</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>45360</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4633.48740324214</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>45354</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>15419.20066074005</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>45385</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12735.51846744415</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>45396</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5916.696127210505</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>45410</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7446.461764212093</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>45295</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1491.487271405857</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15278.19531003341</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>45313</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9800.885695358122</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>45328</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1963.066047472963</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>45343</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>20108.85848963168</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>45331</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>6397.639218261856</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>45377</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1281.41361135346</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13126.2852875303</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>45368</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8128.030771183043</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>45388</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1628.001972034211</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>45396</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>16676.59695842615</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>45408</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ESTOQUE_INICIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11599.09710209025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15599.19746705339</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2554.242097858594</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5969.47320379978</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15492.68846763171</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5474.676462978201</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12647.11732647422</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10445.91090129278</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4852.98503809311</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7943.254362253778</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1590.992225566622</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16297.48401140538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>1.579194433926405</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.440963261053665</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.47476990233223</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0.5624212607928387</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.994791818499178</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.7558894528053292</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.371591709550593</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.386373237222125</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1.22345515541435</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6240949998836578</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.236060491531781</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.357592078564113</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9004634946378404</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.281008603707307</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.5324181198204956</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.84424115775965</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0.6628636117031653</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9218506757585125</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.590491921430324</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0.6616114189338449</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8453209863423212</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>1.056383425793658</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.712377208096453</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.929349092604618</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
